--- a/Result/profitability/1796.xlsx
+++ b/Result/profitability/1796.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01250000000000003</v>
+        <v>0.02749999999999996</v>
       </c>
       <c r="N2" t="n">
-        <v>23.4275</v>
+        <v>24.375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05500000000000003</v>
+        <v>-0.05750000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>23.265</v>
+        <v>24.065</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.12</v>
+        <v>-0.13375</v>
       </c>
       <c r="N4" t="n">
-        <v>22.81625</v>
+        <v>22.77375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1675</v>
+        <v>-0.16375</v>
       </c>
       <c r="N5" t="n">
-        <v>21.63875</v>
+        <v>21.19125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.165</v>
+        <v>-0.17625</v>
       </c>
       <c r="N6" t="n">
-        <v>20.47</v>
+        <v>20.26</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.18375</v>
+        <v>-0.225</v>
       </c>
       <c r="N7" t="n">
-        <v>21.1775</v>
+        <v>20.32375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7798,6 +7798,133 @@
       </c>
       <c r="AM58" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1796</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>169</v>
+      </c>
+      <c r="D59" t="n">
+        <v>127</v>
+      </c>
+      <c r="E59" t="n">
+        <v>42</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.04874999999999997</v>
+      </c>
+      <c r="N59" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-1.3125</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6.690000000000001</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.365174672489083</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>-3.579999999999998</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>-0.1252186079048618</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
